--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,95 +751,172 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2012-09-16</t>
+          <t>2010-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2777</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2777</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2777</v>
-      </c>
-      <c r="Q2" t="n">
+        <v>699</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN2" t="b">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.170747462142559</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -866,17 +943,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -901,95 +978,172 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2012-09-23</t>
+          <t>2010-02-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2010-02</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2198</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2198</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2198</v>
-      </c>
-      <c r="Q3" t="n">
+        <v>600</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.718150133881651</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1016,17 +1170,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1051,95 +1205,172 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2012-09-30</t>
+          <t>2010-03-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2010-03</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2950</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2950</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2950</v>
-      </c>
-      <c r="Q4" t="n">
+        <v>690</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.305979479049532</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1166,17 +1397,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1201,95 +1432,172 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2012-10-07</t>
+          <t>2010-04-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-04</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3161</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3161</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3161</v>
-      </c>
-      <c r="Q5" t="n">
+        <v>550</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.470915638398498</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1624,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1351,95 +1659,172 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2012-10-14</t>
+          <t>2010-05-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-05</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2736</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2736</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2736</v>
-      </c>
-      <c r="Q6" t="n">
+        <v>460</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.138698255823566</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1466,17 +1851,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1501,95 +1886,172 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2012-10-21</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-06</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3550</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3550</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3550</v>
-      </c>
-      <c r="Q7" t="n">
+        <v>332</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.774992254449436</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1616,17 +2078,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1651,95 +2113,172 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2012-10-28</t>
+          <t>2010-07-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2010-07</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3828</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3828</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3828</v>
-      </c>
-      <c r="Q8" t="n">
+        <v>343</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.992301507051392</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1766,17 +2305,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1801,95 +2340,172 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2012-11-04</t>
+          <t>2010-08-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-08</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3859</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3859</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3859</v>
-      </c>
-      <c r="Q9" t="n">
+        <v>418</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>3.016533833780387</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1916,17 +2532,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1951,95 +2567,172 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2012-11-11</t>
+          <t>2010-09-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-09</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5226</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5226</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5226</v>
-      </c>
-      <c r="Q10" t="n">
+        <v>361</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>4.08510127373317</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2759,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2101,95 +2794,172 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2012-11-18</t>
+          <t>2010-10-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-10</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5240</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5240</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5240</v>
-      </c>
-      <c r="Q11" t="n">
+        <v>408</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>4.096044905159168</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2216,17 +2986,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2251,95 +3021,172 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2012-11-25</t>
+          <t>2010-11-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2010-11</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4961</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4961</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4961</v>
-      </c>
-      <c r="Q12" t="n">
+        <v>428</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
-        <v>3.877953964598212</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2366,17 +3213,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2401,95 +3248,172 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2012-12-02</t>
+          <t>2010-12-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5542</v>
-      </c>
-      <c r="O13" t="n">
-        <v>5542</v>
-      </c>
-      <c r="P13" t="n">
-        <v>5542</v>
-      </c>
-      <c r="Q13" t="n">
+        <v>493</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_J02_0_J03_0_STREP_PHARYNGITIS_RANGE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Streptókokka-hálsbólga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for the ICD-10 J02.0-J03.0 range (streptococcal pharyngitis and tonsillitis). The source does not establish Group A etiology, so this series is related to rather than an exact D224 mapping and is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>4.33211466877712</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2551,28 +3475,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2012-12-09</t>
+          <t>2012-09-16</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6485</v>
+        <v>2777</v>
       </c>
       <c r="O14" t="n">
-        <v>6485</v>
+        <v>2777</v>
       </c>
       <c r="P14" t="n">
-        <v>6485</v>
+        <v>2777</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>5.06924641411397</v>
+        <v>2.170747462142559</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2701,28 +3625,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2012-12-16</t>
+          <t>2012-09-23</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6390</v>
+        <v>2198</v>
       </c>
       <c r="O15" t="n">
-        <v>6390</v>
+        <v>2198</v>
       </c>
       <c r="P15" t="n">
-        <v>6390</v>
+        <v>2198</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.994986058008985</v>
+        <v>1.718150133881651</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2851,28 +3775,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2012-12-23</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6898</v>
+        <v>2950</v>
       </c>
       <c r="O16" t="n">
-        <v>6898</v>
+        <v>2950</v>
       </c>
       <c r="P16" t="n">
-        <v>6898</v>
+        <v>2950</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.392083541180904</v>
+        <v>2.305979479049532</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3001,28 +3925,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2012-12-30</t>
+          <t>2012-10-07</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4761</v>
+        <v>3161</v>
       </c>
       <c r="O17" t="n">
-        <v>4761</v>
+        <v>3161</v>
       </c>
       <c r="P17" t="n">
-        <v>4761</v>
+        <v>3161</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.721616372798244</v>
+        <v>2.470915638398498</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3151,28 +4075,28 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2013-01-06</t>
+          <t>2012-10-14</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1587</v>
+        <v>2736</v>
       </c>
       <c r="O18" t="n">
-        <v>1587</v>
+        <v>2736</v>
       </c>
       <c r="P18" t="n">
-        <v>1587</v>
+        <v>2736</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.242526388741386</v>
+        <v>2.138698255823566</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3301,28 +4225,28 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2013-01-13</t>
+          <t>2012-10-21</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4786</v>
+        <v>3550</v>
       </c>
       <c r="O19" t="n">
-        <v>4786</v>
+        <v>3550</v>
       </c>
       <c r="P19" t="n">
-        <v>4786</v>
+        <v>3550</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.747152675813657</v>
+        <v>2.774992254449436</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -3451,28 +4375,28 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2013-01-20</t>
+          <t>2012-10-28</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4762</v>
+        <v>3828</v>
       </c>
       <c r="O20" t="n">
-        <v>4762</v>
+        <v>3828</v>
       </c>
       <c r="P20" t="n">
-        <v>4762</v>
+        <v>3828</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.728362106607739</v>
+        <v>2.992301507051392</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3601,28 +4525,28 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2013-01-27</t>
+          <t>2012-11-04</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>6106</v>
+        <v>3859</v>
       </c>
       <c r="O21" t="n">
-        <v>6106</v>
+        <v>3859</v>
       </c>
       <c r="P21" t="n">
-        <v>6106</v>
+        <v>3859</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.780633982139197</v>
+        <v>3.016533833780387</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3751,28 +4675,28 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2013-02-03</t>
+          <t>2012-11-11</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5908</v>
+        <v>5226</v>
       </c>
       <c r="O22" t="n">
-        <v>5908</v>
+        <v>5226</v>
       </c>
       <c r="P22" t="n">
-        <v>5908</v>
+        <v>5226</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4.625611786190365</v>
+        <v>4.08510127373317</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3901,28 +4825,28 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2013-02-10</t>
+          <t>2012-11-18</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6251</v>
+        <v>5240</v>
       </c>
       <c r="O23" t="n">
-        <v>6251</v>
+        <v>5240</v>
       </c>
       <c r="P23" t="n">
-        <v>6251</v>
+        <v>5240</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.894160337758289</v>
+        <v>4.096044905159168</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -4051,28 +4975,28 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2013-02-17</t>
+          <t>2012-11-25</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>5268</v>
+        <v>4961</v>
       </c>
       <c r="O24" t="n">
-        <v>5268</v>
+        <v>4961</v>
       </c>
       <c r="P24" t="n">
-        <v>5268</v>
+        <v>4961</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.124529940699195</v>
+        <v>3.877953964598212</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -4201,28 +5125,28 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2013-02-24</t>
+          <t>2012-12-02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6931</v>
+        <v>5542</v>
       </c>
       <c r="O25" t="n">
-        <v>6931</v>
+        <v>5542</v>
       </c>
       <c r="P25" t="n">
-        <v>6931</v>
+        <v>5542</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5.426559798592657</v>
+        <v>4.33211466877712</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -4351,28 +5275,28 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2013-03-03</t>
+          <t>2012-12-09</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>7045</v>
+        <v>6485</v>
       </c>
       <c r="O26" t="n">
-        <v>7045</v>
+        <v>6485</v>
       </c>
       <c r="P26" t="n">
-        <v>7045</v>
+        <v>6485</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5.515815002320772</v>
+        <v>5.06924641411397</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -4501,28 +5425,28 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2013-03-10</t>
+          <t>2012-12-16</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>7453</v>
+        <v>6390</v>
       </c>
       <c r="O27" t="n">
-        <v>7453</v>
+        <v>6390</v>
       </c>
       <c r="P27" t="n">
-        <v>7453</v>
+        <v>6390</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5.835254678821394</v>
+        <v>4.994986058008985</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4651,28 +5575,28 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2013-03-17</t>
+          <t>2012-12-23</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7183</v>
+        <v>6898</v>
       </c>
       <c r="O28" t="n">
-        <v>7183</v>
+        <v>6898</v>
       </c>
       <c r="P28" t="n">
-        <v>7183</v>
+        <v>6898</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>5.623860775254806</v>
+        <v>5.392083541180904</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4801,28 +5725,28 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2013-03-24</t>
+          <t>2012-12-30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6139</v>
+        <v>4761</v>
       </c>
       <c r="O29" t="n">
-        <v>6139</v>
+        <v>4761</v>
       </c>
       <c r="P29" t="n">
-        <v>6139</v>
+        <v>4761</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.806471014797334</v>
+        <v>3.721616372798244</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4951,28 +5875,28 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2013-03-31</t>
+          <t>2013-01-06</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>5308</v>
+        <v>1587</v>
       </c>
       <c r="O30" t="n">
-        <v>5308</v>
+        <v>1587</v>
       </c>
       <c r="P30" t="n">
-        <v>5308</v>
+        <v>1587</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.155847556042393</v>
+        <v>1.242526388741386</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5101,28 +6025,28 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2013-04-07</t>
+          <t>2013-01-13</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>4557</v>
+        <v>4786</v>
       </c>
       <c r="O31" t="n">
-        <v>4557</v>
+        <v>4786</v>
       </c>
       <c r="P31" t="n">
-        <v>4557</v>
+        <v>4786</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.567859327973848</v>
+        <v>3.747152675813657</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -5251,28 +6175,28 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2013-04-14</t>
+          <t>2013-01-20</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>5100</v>
+        <v>4762</v>
       </c>
       <c r="O32" t="n">
-        <v>5100</v>
+        <v>4762</v>
       </c>
       <c r="P32" t="n">
-        <v>5100</v>
+        <v>4762</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.992995956257763</v>
+        <v>3.728362106607739</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -5401,28 +6325,28 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2013-04-21</t>
+          <t>2013-01-27</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6616</v>
+        <v>6106</v>
       </c>
       <c r="O33" t="n">
-        <v>6616</v>
+        <v>6106</v>
       </c>
       <c r="P33" t="n">
-        <v>6616</v>
+        <v>6106</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>5.179933577764972</v>
+        <v>4.780633982139197</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -5551,28 +6475,28 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2013-04-28</t>
+          <t>2013-02-03</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>6844</v>
+        <v>5908</v>
       </c>
       <c r="O34" t="n">
-        <v>6844</v>
+        <v>5908</v>
       </c>
       <c r="P34" t="n">
-        <v>6844</v>
+        <v>5908</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>5.358443985221202</v>
+        <v>4.625611786190365</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5701,28 +6625,28 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2013-05-05</t>
+          <t>2013-02-10</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>4303</v>
+        <v>6251</v>
       </c>
       <c r="O35" t="n">
-        <v>4303</v>
+        <v>6251</v>
       </c>
       <c r="P35" t="n">
-        <v>4303</v>
+        <v>6251</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.36899247054454</v>
+        <v>4.894160337758289</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5851,28 +6775,28 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2013-05-12</t>
+          <t>2013-02-17</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>5934</v>
+        <v>5268</v>
       </c>
       <c r="O36" t="n">
-        <v>5934</v>
+        <v>5268</v>
       </c>
       <c r="P36" t="n">
-        <v>5934</v>
+        <v>5268</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.645968236163443</v>
+        <v>4.124529940699195</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6001,28 +6925,28 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2013-05-19</t>
+          <t>2013-02-24</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>7512</v>
+        <v>6931</v>
       </c>
       <c r="O37" t="n">
-        <v>7512</v>
+        <v>6931</v>
       </c>
       <c r="P37" t="n">
-        <v>7512</v>
+        <v>6931</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>5.881448161452611</v>
+        <v>5.426559798592657</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -6151,28 +7075,28 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2013-05-26</t>
+          <t>2013-03-03</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>7276</v>
+        <v>7045</v>
       </c>
       <c r="O38" t="n">
-        <v>7276</v>
+        <v>7045</v>
       </c>
       <c r="P38" t="n">
-        <v>7276</v>
+        <v>7045</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>5.696674230927742</v>
+        <v>5.515815002320772</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6301,28 +7225,28 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2013-06-02</t>
+          <t>2013-03-10</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>7225</v>
+        <v>7453</v>
       </c>
       <c r="O39" t="n">
-        <v>7225</v>
+        <v>7453</v>
       </c>
       <c r="P39" t="n">
-        <v>7225</v>
+        <v>7453</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>5.656744271365164</v>
+        <v>5.835254678821394</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6451,28 +7375,28 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2013-03-17</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>6760</v>
+        <v>7183</v>
       </c>
       <c r="O40" t="n">
-        <v>6760</v>
+        <v>7183</v>
       </c>
       <c r="P40" t="n">
-        <v>6760</v>
+        <v>7183</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>5.292676993000486</v>
+        <v>5.623860775254806</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6601,28 +7525,28 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2013-06-16</t>
+          <t>2013-03-24</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>6817</v>
+        <v>6139</v>
       </c>
       <c r="O41" t="n">
-        <v>6817</v>
+        <v>6139</v>
       </c>
       <c r="P41" t="n">
-        <v>6817</v>
+        <v>6139</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>5.337304594864543</v>
+        <v>4.806471014797334</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6751,28 +7675,28 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2013-06-23</t>
+          <t>2013-03-31</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>5765</v>
+        <v>5308</v>
       </c>
       <c r="O42" t="n">
-        <v>5765</v>
+        <v>5308</v>
       </c>
       <c r="P42" t="n">
-        <v>5765</v>
+        <v>5308</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.513651311338432</v>
+        <v>4.155847556042393</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6901,28 +7825,28 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2013-06-30</t>
+          <t>2013-04-07</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>5611</v>
+        <v>4557</v>
       </c>
       <c r="O43" t="n">
-        <v>5611</v>
+        <v>4557</v>
       </c>
       <c r="P43" t="n">
-        <v>5611</v>
+        <v>4557</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.39307849226712</v>
+        <v>3.567859327973848</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -7051,28 +7975,28 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2013-07-07</t>
+          <t>2013-04-14</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>5043</v>
+        <v>5100</v>
       </c>
       <c r="O44" t="n">
-        <v>5043</v>
+        <v>5100</v>
       </c>
       <c r="P44" t="n">
-        <v>5043</v>
+        <v>5100</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.948368354393706</v>
+        <v>3.992995956257763</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -7201,28 +8125,28 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2013-07-14</t>
+          <t>2013-04-21</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>4543</v>
+        <v>6616</v>
       </c>
       <c r="O45" t="n">
-        <v>4543</v>
+        <v>6616</v>
       </c>
       <c r="P45" t="n">
-        <v>4543</v>
+        <v>6616</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.556898162603729</v>
+        <v>5.179933577764972</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7351,28 +8275,28 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2013-07-21</t>
+          <t>2013-04-28</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3316</v>
+        <v>6844</v>
       </c>
       <c r="O46" t="n">
-        <v>3316</v>
+        <v>6844</v>
       </c>
       <c r="P46" t="n">
-        <v>3316</v>
+        <v>6844</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.596230311951126</v>
+        <v>5.358443985221202</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7501,28 +8425,28 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2013-07-28</t>
+          <t>2013-05-05</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3547</v>
+        <v>4303</v>
       </c>
       <c r="O47" t="n">
-        <v>3547</v>
+        <v>4303</v>
       </c>
       <c r="P47" t="n">
-        <v>3547</v>
+        <v>4303</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.777089540558095</v>
+        <v>3.36899247054454</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7651,28 +8575,28 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2013-08-04</t>
+          <t>2013-05-12</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2982</v>
+        <v>5934</v>
       </c>
       <c r="O48" t="n">
-        <v>2982</v>
+        <v>5934</v>
       </c>
       <c r="P48" t="n">
-        <v>2982</v>
+        <v>5934</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.334728223835421</v>
+        <v>4.645968236163443</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7801,28 +8725,28 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2013-08-11</t>
+          <t>2013-05-19</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2446</v>
+        <v>7512</v>
       </c>
       <c r="O49" t="n">
-        <v>2446</v>
+        <v>7512</v>
       </c>
       <c r="P49" t="n">
-        <v>2446</v>
+        <v>7512</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.915072178236566</v>
+        <v>5.881448161452611</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7951,28 +8875,28 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2013-08-18</t>
+          <t>2013-05-26</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1636</v>
+        <v>7276</v>
       </c>
       <c r="O50" t="n">
-        <v>1636</v>
+        <v>7276</v>
       </c>
       <c r="P50" t="n">
-        <v>1636</v>
+        <v>7276</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.280890467536804</v>
+        <v>5.696674230927742</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -8101,28 +9025,28 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2013-08-25</t>
+          <t>2013-06-02</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1988</v>
+        <v>7225</v>
       </c>
       <c r="O51" t="n">
-        <v>1988</v>
+        <v>7225</v>
       </c>
       <c r="P51" t="n">
-        <v>1988</v>
+        <v>7225</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.556485482556948</v>
+        <v>5.656744271365164</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -8251,28 +9175,28 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2013-09-01</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2126</v>
+        <v>6760</v>
       </c>
       <c r="O52" t="n">
-        <v>2126</v>
+        <v>6760</v>
       </c>
       <c r="P52" t="n">
-        <v>2126</v>
+        <v>6760</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.664531255490981</v>
+        <v>5.292676993000486</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8401,28 +9325,28 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2013-09-08</t>
+          <t>2013-06-16</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2447</v>
+        <v>6817</v>
       </c>
       <c r="O53" t="n">
-        <v>2447</v>
+        <v>6817</v>
       </c>
       <c r="P53" t="n">
-        <v>2447</v>
+        <v>6817</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.915855118620146</v>
+        <v>5.337304594864543</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -8551,28 +9475,28 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
+          <t>2013-06-23</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2682</v>
+        <v>5765</v>
       </c>
       <c r="O54" t="n">
-        <v>2682</v>
+        <v>5765</v>
       </c>
       <c r="P54" t="n">
-        <v>2682</v>
+        <v>5765</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.099846108761435</v>
+        <v>4.513651311338432</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8701,28 +9625,28 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2013-09-22</t>
+          <t>2013-06-30</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2306</v>
+        <v>5611</v>
       </c>
       <c r="O55" t="n">
-        <v>2306</v>
+        <v>5611</v>
       </c>
       <c r="P55" t="n">
-        <v>2306</v>
+        <v>5611</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.805460524535373</v>
+        <v>4.39307849226712</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8851,28 +9775,28 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2013-09-29</t>
+          <t>2013-07-07</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2273</v>
+        <v>5043</v>
       </c>
       <c r="O56" t="n">
-        <v>2273</v>
+        <v>5043</v>
       </c>
       <c r="P56" t="n">
-        <v>2273</v>
+        <v>5043</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.779623491877234</v>
+        <v>3.948368354393706</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9001,28 +9925,28 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2013-10-06</t>
+          <t>2013-07-14</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>3017</v>
+        <v>4543</v>
       </c>
       <c r="O57" t="n">
-        <v>3017</v>
+        <v>4543</v>
       </c>
       <c r="P57" t="n">
-        <v>3017</v>
+        <v>4543</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.362131137260719</v>
+        <v>3.556898162603729</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9151,28 +10075,28 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
+          <t>2013-07-21</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>3103</v>
+        <v>3316</v>
       </c>
       <c r="O58" t="n">
-        <v>3103</v>
+        <v>3316</v>
       </c>
       <c r="P58" t="n">
-        <v>3103</v>
+        <v>3316</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.429464010248596</v>
+        <v>2.596230311951126</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -9301,28 +10225,28 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-07-28</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2397</v>
+        <v>3547</v>
       </c>
       <c r="O59" t="n">
-        <v>2397</v>
+        <v>3547</v>
       </c>
       <c r="P59" t="n">
-        <v>2397</v>
+        <v>3547</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.876708099441149</v>
+        <v>2.777089540558095</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -9451,28 +10375,28 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-08-04</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>3467</v>
+        <v>2982</v>
       </c>
       <c r="O60" t="n">
-        <v>3467</v>
+        <v>2982</v>
       </c>
       <c r="P60" t="n">
-        <v>3467</v>
+        <v>2982</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.714454309871699</v>
+        <v>2.334728223835421</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -9601,28 +10525,28 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-08-11</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3670</v>
+        <v>2446</v>
       </c>
       <c r="O61" t="n">
-        <v>3670</v>
+        <v>2446</v>
       </c>
       <c r="P61" t="n">
-        <v>3670</v>
+        <v>2446</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.873391207738429</v>
+        <v>1.915072178236566</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -9751,28 +10675,28 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2013-11-10</t>
+          <t>2013-08-18</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3480</v>
+        <v>1636</v>
       </c>
       <c r="O62" t="n">
-        <v>3480</v>
+        <v>1636</v>
       </c>
       <c r="P62" t="n">
-        <v>3480</v>
+        <v>1636</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.724632534858238</v>
+        <v>1.280890467536804</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -9901,28 +10825,28 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2013-11-17</t>
+          <t>2013-08-25</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>4278</v>
+        <v>1988</v>
       </c>
       <c r="O63" t="n">
-        <v>4278</v>
+        <v>1988</v>
       </c>
       <c r="P63" t="n">
-        <v>4278</v>
+        <v>1988</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.349418960955041</v>
+        <v>1.556485482556948</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -10051,28 +10975,28 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2013-11-24</t>
+          <t>2013-09-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>4667</v>
+        <v>2126</v>
       </c>
       <c r="O64" t="n">
-        <v>4667</v>
+        <v>2126</v>
       </c>
       <c r="P64" t="n">
-        <v>4667</v>
+        <v>2126</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.653982770167643</v>
+        <v>1.664531255490981</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -10201,28 +11125,28 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-09-08</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>5982</v>
+        <v>2447</v>
       </c>
       <c r="O65" t="n">
-        <v>5982</v>
+        <v>2447</v>
       </c>
       <c r="P65" t="n">
-        <v>5982</v>
+        <v>2447</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>4.683549374575281</v>
+        <v>1.915855118620146</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -10351,28 +11275,28 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2013-12-08</t>
+          <t>2013-09-15</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>6569</v>
+        <v>2682</v>
       </c>
       <c r="O66" t="n">
-        <v>6569</v>
+        <v>2682</v>
       </c>
       <c r="P66" t="n">
-        <v>6569</v>
+        <v>2682</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.143135379736714</v>
+        <v>2.099846108761435</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -10501,28 +11425,28 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2013-12-15</t>
+          <t>2013-09-22</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>7177</v>
+        <v>2306</v>
       </c>
       <c r="O67" t="n">
-        <v>7177</v>
+        <v>2306</v>
       </c>
       <c r="P67" t="n">
-        <v>7177</v>
+        <v>2306</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>5.619163132953326</v>
+        <v>1.805460524535373</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10651,28 +11575,28 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2013-12-22</t>
+          <t>2013-09-29</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>7460</v>
+        <v>2273</v>
       </c>
       <c r="O68" t="n">
-        <v>7460</v>
+        <v>2273</v>
       </c>
       <c r="P68" t="n">
-        <v>7460</v>
+        <v>2273</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>5.840735261506453</v>
+        <v>1.779623491877234</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10801,28 +11725,28 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2013-12-29</t>
+          <t>2013-10-06</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>5440</v>
+        <v>3017</v>
       </c>
       <c r="O69" t="n">
-        <v>5440</v>
+        <v>3017</v>
       </c>
       <c r="P69" t="n">
-        <v>5440</v>
+        <v>3017</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>4.259195686674947</v>
+        <v>2.362131137260719</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -10951,28 +11875,28 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2014-01-05</t>
+          <t>2013-10-13</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1584</v>
+        <v>3103</v>
       </c>
       <c r="O70" t="n">
-        <v>1584</v>
+        <v>3103</v>
       </c>
       <c r="P70" t="n">
-        <v>1584</v>
+        <v>3103</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.242483479901608</v>
+        <v>2.429464010248596</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -11101,28 +12025,28 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2014-01-12</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>5082</v>
+        <v>2397</v>
       </c>
       <c r="O71" t="n">
-        <v>5082</v>
+        <v>2397</v>
       </c>
       <c r="P71" t="n">
-        <v>5082</v>
+        <v>2397</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.986301164684326</v>
+        <v>1.876708099441149</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -11251,28 +12175,28 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2014-01-19</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>5319</v>
+        <v>3467</v>
       </c>
       <c r="O72" t="n">
-        <v>5319</v>
+        <v>3467</v>
       </c>
       <c r="P72" t="n">
-        <v>5319</v>
+        <v>3467</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.172203048987786</v>
+        <v>2.714454309871699</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -11401,28 +12325,28 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2014-01-26</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>6898</v>
+        <v>3670</v>
       </c>
       <c r="O73" t="n">
-        <v>6898</v>
+        <v>3670</v>
       </c>
       <c r="P73" t="n">
-        <v>6898</v>
+        <v>3670</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>5.410764548207887</v>
+        <v>2.873391207738429</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -11551,28 +12475,28 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2014-02-02</t>
+          <t>2013-11-10</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>6792</v>
+        <v>3480</v>
       </c>
       <c r="O74" t="n">
-        <v>6792</v>
+        <v>3480</v>
       </c>
       <c r="P74" t="n">
-        <v>6792</v>
+        <v>3480</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>5.327618557759925</v>
+        <v>2.724632534858238</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -11701,28 +12625,28 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2014-02-09</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>6425</v>
+        <v>4278</v>
       </c>
       <c r="O75" t="n">
-        <v>6425</v>
+        <v>4278</v>
       </c>
       <c r="P75" t="n">
-        <v>6425</v>
+        <v>4278</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>5.039745175737267</v>
+        <v>3.349418960955041</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -11851,28 +12775,28 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2013-11-24</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5498</v>
+        <v>4667</v>
       </c>
       <c r="O76" t="n">
-        <v>5498</v>
+        <v>4667</v>
       </c>
       <c r="P76" t="n">
-        <v>5498</v>
+        <v>4667</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.312609957385758</v>
+        <v>3.653982770167643</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -12001,28 +12925,28 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2014-02-23</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>6722</v>
+        <v>5982</v>
       </c>
       <c r="O77" t="n">
-        <v>6722</v>
+        <v>5982</v>
       </c>
       <c r="P77" t="n">
-        <v>6722</v>
+        <v>5982</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>5.272710828218819</v>
+        <v>4.683549374575281</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -12151,28 +13075,28 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2014-03-02</t>
+          <t>2013-12-08</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>7222</v>
+        <v>6569</v>
       </c>
       <c r="O78" t="n">
-        <v>7222</v>
+        <v>6569</v>
       </c>
       <c r="P78" t="n">
-        <v>7222</v>
+        <v>6569</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>5.664908896369579</v>
+        <v>5.143135379736714</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -12301,28 +13225,28 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2014-03-09</t>
+          <t>2013-12-15</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>6894</v>
+        <v>7177</v>
       </c>
       <c r="O79" t="n">
-        <v>6894</v>
+        <v>7177</v>
       </c>
       <c r="P79" t="n">
-        <v>6894</v>
+        <v>7177</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>5.40762696366268</v>
+        <v>5.619163132953326</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -12451,28 +13375,28 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2014-03-16</t>
+          <t>2013-12-22</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>6773</v>
+        <v>7460</v>
       </c>
       <c r="O80" t="n">
-        <v>6773</v>
+        <v>7460</v>
       </c>
       <c r="P80" t="n">
-        <v>6773</v>
+        <v>7460</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>5.312715031170196</v>
+        <v>5.840735261506453</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -12601,28 +13525,28 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2014-03-23</t>
+          <t>2013-12-29</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>5767</v>
+        <v>5440</v>
       </c>
       <c r="O81" t="n">
-        <v>5767</v>
+        <v>5440</v>
       </c>
       <c r="P81" t="n">
-        <v>5767</v>
+        <v>5440</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.523612518050867</v>
+        <v>4.259195686674947</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -12751,28 +13675,28 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2014-03-30</t>
+          <t>2014-01-05</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>5269</v>
+        <v>1584</v>
       </c>
       <c r="O82" t="n">
-        <v>5269</v>
+        <v>1584</v>
       </c>
       <c r="P82" t="n">
-        <v>5269</v>
+        <v>1584</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.13298324217271</v>
+        <v>1.242483479901608</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -12901,28 +13825,28 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2014-04-06</t>
+          <t>2014-01-12</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>4519</v>
+        <v>5082</v>
       </c>
       <c r="O83" t="n">
-        <v>4519</v>
+        <v>5082</v>
       </c>
       <c r="P83" t="n">
-        <v>4519</v>
+        <v>5082</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.54468613994657</v>
+        <v>3.986301164684326</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -13051,28 +13975,28 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2014-04-13</t>
+          <t>2014-01-19</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>5014</v>
+        <v>5319</v>
       </c>
       <c r="O84" t="n">
-        <v>5014</v>
+        <v>5319</v>
       </c>
       <c r="P84" t="n">
-        <v>5014</v>
+        <v>5319</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.932962227415822</v>
+        <v>4.172203048987786</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -13201,28 +14125,28 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2014-04-20</t>
+          <t>2014-01-26</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>6679</v>
+        <v>6898</v>
       </c>
       <c r="O85" t="n">
-        <v>6679</v>
+        <v>6898</v>
       </c>
       <c r="P85" t="n">
-        <v>6679</v>
+        <v>6898</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>5.238981794357853</v>
+        <v>5.410764548207887</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -13351,28 +14275,28 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2014-04-27</t>
+          <t>2014-02-02</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>7423</v>
+        <v>6792</v>
       </c>
       <c r="O86" t="n">
-        <v>7423</v>
+        <v>6792</v>
       </c>
       <c r="P86" t="n">
-        <v>7423</v>
+        <v>6792</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>5.822572519766184</v>
+        <v>5.327618557759925</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -13501,28 +14425,28 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2014-05-04</t>
+          <t>2014-02-09</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>6044</v>
+        <v>6425</v>
       </c>
       <c r="O87" t="n">
-        <v>6044</v>
+        <v>6425</v>
       </c>
       <c r="P87" t="n">
-        <v>6044</v>
+        <v>6425</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>4.740890247806388</v>
+        <v>5.039745175737267</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -13651,28 +14575,28 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2014-05-11</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>5139</v>
+        <v>5498</v>
       </c>
       <c r="O88" t="n">
-        <v>5139</v>
+        <v>5498</v>
       </c>
       <c r="P88" t="n">
-        <v>5139</v>
+        <v>5498</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.031011744453512</v>
+        <v>4.312609957385758</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -13801,28 +14725,28 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2014-05-18</t>
+          <t>2014-02-23</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>8783</v>
+        <v>6722</v>
       </c>
       <c r="O89" t="n">
-        <v>8783</v>
+        <v>6722</v>
       </c>
       <c r="P89" t="n">
-        <v>8783</v>
+        <v>6722</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>6.889351265136251</v>
+        <v>5.272710828218819</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -13951,28 +14875,28 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2014-05-25</t>
+          <t>2014-03-02</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>9049</v>
+        <v>7222</v>
       </c>
       <c r="O90" t="n">
-        <v>9049</v>
+        <v>7222</v>
       </c>
       <c r="P90" t="n">
-        <v>9049</v>
+        <v>7222</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>7.098000637392457</v>
+        <v>5.664908896369579</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -14101,28 +15025,28 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
+          <t>2014-03-09</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>9252</v>
+        <v>6894</v>
       </c>
       <c r="O91" t="n">
-        <v>9252</v>
+        <v>6894</v>
       </c>
       <c r="P91" t="n">
-        <v>9252</v>
+        <v>6894</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>7.257233053061666</v>
+        <v>5.40762696366268</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -14251,28 +15175,28 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2014-06-08</t>
+          <t>2014-03-16</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>8269</v>
+        <v>6773</v>
       </c>
       <c r="O92" t="n">
-        <v>8269</v>
+        <v>6773</v>
       </c>
       <c r="P92" t="n">
-        <v>8269</v>
+        <v>6773</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>6.486171651077271</v>
+        <v>5.312715031170196</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -14401,28 +15325,28 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2014-06-15</t>
+          <t>2014-03-23</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>8048</v>
+        <v>5767</v>
       </c>
       <c r="O93" t="n">
-        <v>8048</v>
+        <v>5767</v>
       </c>
       <c r="P93" t="n">
-        <v>8048</v>
+        <v>5767</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>6.312820104954636</v>
+        <v>4.523612518050867</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -14551,28 +15475,28 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2014-06-22</t>
+          <t>2014-03-30</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>7783</v>
+        <v>5269</v>
       </c>
       <c r="O94" t="n">
-        <v>7783</v>
+        <v>5269</v>
       </c>
       <c r="P94" t="n">
-        <v>7783</v>
+        <v>5269</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>6.104955128834732</v>
+        <v>4.13298324217271</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -14701,28 +15625,28 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-04-06</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>7436</v>
+        <v>4519</v>
       </c>
       <c r="O95" t="n">
-        <v>7436</v>
+        <v>4519</v>
       </c>
       <c r="P95" t="n">
-        <v>7436</v>
+        <v>4519</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>5.832769669538105</v>
+        <v>3.54468613994657</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -14851,28 +15775,28 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2014-07-06</t>
+          <t>2014-04-13</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>6705</v>
+        <v>5014</v>
       </c>
       <c r="O96" t="n">
-        <v>6705</v>
+        <v>5014</v>
       </c>
       <c r="P96" t="n">
-        <v>6705</v>
+        <v>5014</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>5.259376093901693</v>
+        <v>3.932962227415822</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -15001,28 +15925,28 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2014-07-13</t>
+          <t>2014-04-20</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>6268</v>
+        <v>6679</v>
       </c>
       <c r="O97" t="n">
-        <v>6268</v>
+        <v>6679</v>
       </c>
       <c r="P97" t="n">
-        <v>6268</v>
+        <v>6679</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>4.916594982337928</v>
+        <v>5.238981794357853</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -15151,28 +16075,28 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2014-07-20</t>
+          <t>2014-04-27</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>5243</v>
+        <v>7423</v>
       </c>
       <c r="O98" t="n">
-        <v>5243</v>
+        <v>7423</v>
       </c>
       <c r="P98" t="n">
-        <v>5243</v>
+        <v>7423</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>4.112588942628871</v>
+        <v>5.822572519766184</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -15301,28 +16225,28 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2014-07-27</t>
+          <t>2014-05-04</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>3604</v>
+        <v>6044</v>
       </c>
       <c r="O99" t="n">
-        <v>3604</v>
+        <v>6044</v>
       </c>
       <c r="P99" t="n">
-        <v>3604</v>
+        <v>6044</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.826963675230679</v>
+        <v>4.740890247806388</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -15451,28 +16375,28 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2014-08-03</t>
+          <t>2014-05-11</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3427</v>
+        <v>5139</v>
       </c>
       <c r="O100" t="n">
-        <v>3427</v>
+        <v>5139</v>
       </c>
       <c r="P100" t="n">
-        <v>3427</v>
+        <v>5139</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.68812555910531</v>
+        <v>4.031011744453512</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -15601,28 +16525,28 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2014-08-10</t>
+          <t>2014-05-18</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2923</v>
+        <v>8783</v>
       </c>
       <c r="O101" t="n">
-        <v>2923</v>
+        <v>8783</v>
       </c>
       <c r="P101" t="n">
-        <v>2923</v>
+        <v>8783</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.292789906409344</v>
+        <v>6.889351265136251</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -15751,28 +16675,28 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2014-08-17</t>
+          <t>2014-05-25</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1867</v>
+        <v>9049</v>
       </c>
       <c r="O102" t="n">
-        <v>1867</v>
+        <v>9049</v>
       </c>
       <c r="P102" t="n">
-        <v>1867</v>
+        <v>9049</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1.464467586474938</v>
+        <v>7.098000637392457</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -15901,28 +16825,28 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2014-08-24</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2419</v>
+        <v>9252</v>
       </c>
       <c r="O103" t="n">
-        <v>2419</v>
+        <v>9252</v>
       </c>
       <c r="P103" t="n">
-        <v>2419</v>
+        <v>9252</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>1.897454253713377</v>
+        <v>7.257233053061666</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -16051,28 +16975,28 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2014-06-08</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2612</v>
+        <v>8269</v>
       </c>
       <c r="O104" t="n">
-        <v>2612</v>
+        <v>8269</v>
       </c>
       <c r="P104" t="n">
-        <v>2612</v>
+        <v>8269</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.048842708019571</v>
+        <v>6.486171651077271</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -16201,28 +17125,28 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2014-06-15</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>3098</v>
+        <v>8048</v>
       </c>
       <c r="O105" t="n">
-        <v>3098</v>
+        <v>8048</v>
       </c>
       <c r="P105" t="n">
-        <v>3098</v>
+        <v>8048</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.430059230262109</v>
+        <v>6.312820104954636</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -16351,28 +17275,28 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2014-06-22</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>3415</v>
+        <v>7783</v>
       </c>
       <c r="O106" t="n">
-        <v>3415</v>
+        <v>7783</v>
       </c>
       <c r="P106" t="n">
-        <v>3415</v>
+        <v>7783</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.678712805469691</v>
+        <v>6.104955128834732</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -16501,28 +17425,28 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2014-09-21</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>3097</v>
+        <v>7436</v>
       </c>
       <c r="O107" t="n">
-        <v>3097</v>
+        <v>7436</v>
       </c>
       <c r="P107" t="n">
-        <v>3097</v>
+        <v>7436</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.429274834125808</v>
+        <v>5.832769669538105</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -16651,28 +17575,28 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2014-09-28</t>
+          <t>2014-07-06</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>3740</v>
+        <v>6705</v>
       </c>
       <c r="O108" t="n">
-        <v>3740</v>
+        <v>6705</v>
       </c>
       <c r="P108" t="n">
-        <v>3740</v>
+        <v>6705</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.933641549767685</v>
+        <v>5.259376093901693</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -16801,28 +17725,28 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2014-10-05</t>
+          <t>2014-07-13</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>3975</v>
+        <v>6268</v>
       </c>
       <c r="O109" t="n">
-        <v>3975</v>
+        <v>6268</v>
       </c>
       <c r="P109" t="n">
-        <v>3975</v>
+        <v>6268</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.117974641798543</v>
+        <v>4.916594982337928</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -16951,28 +17875,28 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2014-10-12</t>
+          <t>2014-07-20</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>3996</v>
+        <v>5243</v>
       </c>
       <c r="O110" t="n">
-        <v>3996</v>
+        <v>5243</v>
       </c>
       <c r="P110" t="n">
-        <v>3996</v>
+        <v>5243</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.134446960660875</v>
+        <v>4.112588942628871</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -17101,28 +18025,28 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2014-10-19</t>
+          <t>2014-07-27</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>3736</v>
+        <v>3604</v>
       </c>
       <c r="O111" t="n">
-        <v>3736</v>
+        <v>3604</v>
       </c>
       <c r="P111" t="n">
-        <v>3736</v>
+        <v>3604</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.93050396522248</v>
+        <v>2.826963675230679</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -17251,28 +18175,28 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2014-10-26</t>
+          <t>2014-08-03</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>5225</v>
+        <v>3427</v>
       </c>
       <c r="O112" t="n">
-        <v>5225</v>
+        <v>3427</v>
       </c>
       <c r="P112" t="n">
-        <v>5225</v>
+        <v>3427</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>4.098469812175443</v>
+        <v>2.68812555910531</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -17401,28 +18325,28 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2014-11-02</t>
+          <t>2014-08-10</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>5973</v>
+        <v>2923</v>
       </c>
       <c r="O113" t="n">
-        <v>5973</v>
+        <v>2923</v>
       </c>
       <c r="P113" t="n">
-        <v>5973</v>
+        <v>2923</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>4.68519812212898</v>
+        <v>2.292789906409344</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -17551,28 +18475,28 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2014-11-09</t>
+          <t>2014-08-17</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>5346</v>
+        <v>1867</v>
       </c>
       <c r="O114" t="n">
-        <v>5346</v>
+        <v>1867</v>
       </c>
       <c r="P114" t="n">
-        <v>5346</v>
+        <v>1867</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>4.193381744667927</v>
+        <v>1.464467586474938</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -17701,28 +18625,28 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2014-11-16</t>
+          <t>2014-08-24</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>6822</v>
+        <v>2419</v>
       </c>
       <c r="O115" t="n">
-        <v>6822</v>
+        <v>2419</v>
       </c>
       <c r="P115" t="n">
-        <v>6822</v>
+        <v>2419</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>5.35115044184897</v>
+        <v>1.897454253713377</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -17851,28 +18775,28 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2014-11-23</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>7781</v>
+        <v>2612</v>
       </c>
       <c r="O116" t="n">
-        <v>7781</v>
+        <v>2612</v>
       </c>
       <c r="P116" t="n">
-        <v>7781</v>
+        <v>2612</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>6.103386336562129</v>
+        <v>2.048842708019571</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -18001,28 +18925,28 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2014-11-30</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>7554</v>
+        <v>3098</v>
       </c>
       <c r="O117" t="n">
-        <v>7554</v>
+        <v>3098</v>
       </c>
       <c r="P117" t="n">
-        <v>7554</v>
+        <v>3098</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>5.925328413621684</v>
+        <v>2.430059230262109</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -18151,28 +19075,28 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2014-12-07</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>8894</v>
+        <v>3415</v>
       </c>
       <c r="O118" t="n">
-        <v>8894</v>
+        <v>3415</v>
       </c>
       <c r="P118" t="n">
-        <v>8894</v>
+        <v>3415</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>6.976419236265721</v>
+        <v>2.678712805469691</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -18301,28 +19225,28 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2014-12-14</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>9419</v>
+        <v>3097</v>
       </c>
       <c r="O119" t="n">
-        <v>9419</v>
+        <v>3097</v>
       </c>
       <c r="P119" t="n">
-        <v>9419</v>
+        <v>3097</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>7.38822720782402</v>
+        <v>2.429274834125808</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -18451,28 +19375,28 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2014-12-21</t>
+          <t>2014-09-28</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>9082</v>
+        <v>3740</v>
       </c>
       <c r="O120" t="n">
-        <v>9082</v>
+        <v>3740</v>
       </c>
       <c r="P120" t="n">
-        <v>9082</v>
+        <v>3740</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>7.123885709890406</v>
+        <v>2.933641549767685</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -18601,28 +19525,28 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2014-12-28</t>
+          <t>2014-10-05</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>7256</v>
+        <v>3975</v>
       </c>
       <c r="O121" t="n">
-        <v>7256</v>
+        <v>3975</v>
       </c>
       <c r="P121" t="n">
-        <v>7256</v>
+        <v>3975</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>5.691578365003831</v>
+        <v>3.117974641798543</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -18688,6 +19612,1806 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2014-10-12</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>3996</v>
+      </c>
+      <c r="O122" t="n">
+        <v>3996</v>
+      </c>
+      <c r="P122" t="n">
+        <v>3996</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>3.134446960660875</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2014-10-19</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>3736</v>
+      </c>
+      <c r="O123" t="n">
+        <v>3736</v>
+      </c>
+      <c r="P123" t="n">
+        <v>3736</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>2.93050396522248</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2014-10-26</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>5225</v>
+      </c>
+      <c r="O124" t="n">
+        <v>5225</v>
+      </c>
+      <c r="P124" t="n">
+        <v>5225</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>4.098469812175443</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2014-11-02</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>5973</v>
+      </c>
+      <c r="O125" t="n">
+        <v>5973</v>
+      </c>
+      <c r="P125" t="n">
+        <v>5973</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>4.68519812212898</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2014-11-09</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>5346</v>
+      </c>
+      <c r="O126" t="n">
+        <v>5346</v>
+      </c>
+      <c r="P126" t="n">
+        <v>5346</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4.193381744667927</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2014-11-16</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>6822</v>
+      </c>
+      <c r="O127" t="n">
+        <v>6822</v>
+      </c>
+      <c r="P127" t="n">
+        <v>6822</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>5.35115044184897</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2014-11-23</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>7781</v>
+      </c>
+      <c r="O128" t="n">
+        <v>7781</v>
+      </c>
+      <c r="P128" t="n">
+        <v>7781</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6.103386336562129</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2014-11-30</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>7554</v>
+      </c>
+      <c r="O129" t="n">
+        <v>7554</v>
+      </c>
+      <c r="P129" t="n">
+        <v>7554</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>5.925328413621684</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2014-12-07</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>8894</v>
+      </c>
+      <c r="O130" t="n">
+        <v>8894</v>
+      </c>
+      <c r="P130" t="n">
+        <v>8894</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6.976419236265721</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2014-12-14</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>9419</v>
+      </c>
+      <c r="O131" t="n">
+        <v>9419</v>
+      </c>
+      <c r="P131" t="n">
+        <v>9419</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7.38822720782402</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2014-12-21</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>9082</v>
+      </c>
+      <c r="O132" t="n">
+        <v>9082</v>
+      </c>
+      <c r="P132" t="n">
+        <v>9082</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7.123885709890406</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>group-a-streptococcal-pharyngitis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D224</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Group A streptococcal pharyngitis</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>A族链球菌性咽炎</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2014-12-28</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>7256</v>
+      </c>
+      <c r="O133" t="n">
+        <v>7256</v>
+      </c>
+      <c r="P133" t="n">
+        <v>7256</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>5.691578365003831</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_JP_GAS_PHARYNGITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18738,7 +21462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2012-09-16</t>
+          <t>2010-01-01</t>
         </is>
       </c>
     </row>
@@ -18819,7 +21543,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -18839,7 +21563,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -18849,7 +21573,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
